--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/oct-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26421,7 +26421,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27275,7 +27275,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27641,7 +27641,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28739,7 +28739,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28861,7 +28861,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29593,7 +29593,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29837,7 +29837,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31194,7 +31194,7 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -31244,7 +31244,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31427,7 +31427,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31549,7 +31549,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31671,7 +31671,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31732,7 +31732,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31793,7 +31793,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31854,7 +31854,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31976,7 +31976,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32098,7 +32098,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32159,7 +32159,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32342,7 +32342,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32525,7 +32525,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32647,7 +32647,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32952,7 +32952,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33074,7 +33074,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33135,7 +33135,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33196,7 +33196,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33257,7 +33257,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33501,7 +33501,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33623,7 +33623,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33928,7 +33928,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33989,7 +33989,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34111,7 +34111,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34294,7 +34294,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34355,7 +34355,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34477,7 +34477,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34721,7 +34721,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34843,7 +34843,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34904,7 +34904,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34965,7 +34965,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35087,7 +35087,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35209,7 +35209,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35270,7 +35270,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35331,7 +35331,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35514,7 +35514,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35575,7 +35575,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35697,7 +35697,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36246,7 +36246,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36307,7 +36307,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36368,7 +36368,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36490,7 +36490,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36551,7 +36551,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36612,7 +36612,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36734,7 +36734,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36795,7 +36795,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36856,7 +36856,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36917,7 +36917,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36978,7 +36978,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37039,7 +37039,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37161,7 +37161,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37283,7 +37283,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37344,7 +37344,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37405,7 +37405,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37588,7 +37588,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37649,7 +37649,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37771,7 +37771,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37893,7 +37893,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -38015,7 +38015,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38076,7 +38076,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38259,7 +38259,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38320,7 +38320,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38381,7 +38381,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38442,7 +38442,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38503,7 +38503,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38564,7 +38564,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38625,7 +38625,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38686,7 +38686,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38808,7 +38808,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38869,7 +38869,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39113,7 +39113,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39174,7 +39174,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39235,7 +39235,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39296,7 +39296,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39418,7 +39418,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39540,7 +39540,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39723,7 +39723,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39845,7 +39845,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39906,7 +39906,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40028,7 +40028,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40089,7 +40089,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40150,7 +40150,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40272,7 +40272,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40394,7 +40394,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40455,7 +40455,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40516,7 +40516,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40577,7 +40577,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40638,7 +40638,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40821,7 +40821,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40882,7 +40882,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40943,7 +40943,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41065,7 +41065,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41187,7 +41187,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41309,7 +41309,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41431,7 +41431,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41492,7 +41492,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41553,7 +41553,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41675,7 +41675,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41736,7 +41736,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41797,7 +41797,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41919,7 +41919,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41980,7 +41980,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42041,7 +42041,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42102,7 +42102,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42224,7 +42224,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42346,7 +42346,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42407,7 +42407,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42590,7 +42590,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42651,7 +42651,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42712,7 +42712,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42773,7 +42773,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43017,7 +43017,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/oct-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/oct-2025.xlsx
@@ -623,7 +623,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2139,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2204,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2334,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2586,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2964,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3029,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3224,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3411,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3789,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3980,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4045,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4175,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4240,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4492,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4683,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4748,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5057,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5183,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5309,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5374,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5500,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5565,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5695,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5821,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6008,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6073,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6199,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6264,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6329,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6455,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6581,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6646,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6776,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +6967,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7032,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7097,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7162,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7353,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7540,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7666,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7796,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7861,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8048,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8235,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8300,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8426,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8491,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8678,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8930,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +8995,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9247,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9312,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9377,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9442,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9507,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9637,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9763,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10259,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10446,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10511,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10576,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10702,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10828,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +10954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11019,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11145,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11210,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11523,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11840,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12149,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12462,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12527,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12657,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12722,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12852,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +12978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13043,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13539,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13604,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13730,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13795,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13860,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14047,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14421,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14734,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +14925,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +14990,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15055,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15181,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15246,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15433,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15498,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15624,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15689,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +15815,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16246,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16311,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16498,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16563,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16628,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16693,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +16758,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +16823,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +16888,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +16953,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17201,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17266,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17331,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17461,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17713,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +17961,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18026,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18091,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18339,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18404,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18656,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19026,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19152,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19217,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19343,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19469,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19534,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19721,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +19847,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +19973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20038,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20103,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20168,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20359,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20546,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20676,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +20863,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +20928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +20993,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21058,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21184,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21249,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21379,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21692,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +21757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +21822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +21887,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +21952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22078,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22143,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22208,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22273,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22399,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22525,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22590,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +22777,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +22842,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23029,11 @@
           <t>77.550.346-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23159,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23415,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23480,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23545,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23610,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +23675,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +23801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +23927,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24053,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24244,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +25053,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25301,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +25427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +25675,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +25740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +25805,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +25870,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +25996,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25153,7 +26061,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +26126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +26252,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25397,7 +26317,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25458,7 +26382,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +26447,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +26512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25641,7 +26577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +26703,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +26768,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26068,7 +27016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26129,7 +27081,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27207,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26556,7 +27516,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26617,7 +27581,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +27646,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +27711,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26800,7 +27776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26861,7 +27841,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +27967,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +28032,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27105,7 +28097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27166,7 +28162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27349,7 +28349,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27532,7 +28536,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27654,7 +28662,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27715,7 +28727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27898,7 +28914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27959,7 +28979,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28142,7 +29166,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28203,7 +29231,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28264,7 +29296,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +29422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +29487,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28508,7 +29552,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +29617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +29743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28752,7 +29808,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28813,7 +29873,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28935,7 +29999,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +30064,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29057,7 +30129,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +30194,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29179,7 +30259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29362,7 +30446,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29423,7 +30511,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +30576,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29545,7 +30641,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +30706,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29667,7 +30771,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29728,7 +30836,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +30901,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29850,7 +30966,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29911,7 +31031,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30033,7 +31157,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30094,7 +31222,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30155,7 +31287,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30216,7 +31352,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30277,7 +31417,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30338,7 +31482,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30399,7 +31547,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30521,7 +31673,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30643,7 +31799,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30826,7 +31986,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30887,7 +32051,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30948,7 +32116,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31070,7 +32242,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31379,7 +32555,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31501,7 +32681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31623,7 +32807,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31684,7 +32872,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31806,7 +32998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31928,7 +33124,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32050,7 +33250,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32111,7 +33315,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32172,7 +33380,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32294,7 +33506,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32416,7 +33632,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32477,7 +33697,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32538,7 +33762,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32599,7 +33827,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32721,7 +33953,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32843,7 +34079,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32965,7 +34205,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33026,7 +34270,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33148,7 +34396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33270,7 +34522,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33331,7 +34587,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33453,7 +34713,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33575,7 +34839,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33636,7 +34904,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33697,7 +34969,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33758,7 +35034,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33880,7 +35160,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33941,7 +35225,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34063,7 +35351,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34185,7 +35477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34246,7 +35542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34429,7 +35729,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34612,7 +35916,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34734,7 +36042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34795,7 +36107,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34856,7 +36172,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34917,7 +36237,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34978,7 +36302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35039,7 +36367,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35100,7 +36432,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35161,7 +36497,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35283,7 +36623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35344,7 +36688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35405,7 +36753,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35466,7 +36818,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35527,7 +36883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35588,7 +36948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35710,7 +37074,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35832,7 +37200,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35893,7 +37265,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36015,7 +37391,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36076,7 +37456,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36198,7 +37582,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36381,7 +37769,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36442,7 +37834,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36503,7 +37899,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36564,7 +37964,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36930,7 +38334,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37052,7 +38460,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37113,7 +38525,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37174,7 +38590,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37296,7 +38716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37357,7 +38781,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37418,7 +38846,11 @@
           <t>77.550.346-7</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37479,7 +38911,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37662,7 +39098,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37723,7 +39163,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37845,7 +39289,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37906,7 +39354,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38211,7 +39663,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38333,7 +39789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38394,7 +39854,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38455,7 +39919,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38577,7 +40045,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38699,7 +40171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38760,7 +40236,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38882,7 +40362,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38943,7 +40427,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39004,7 +40492,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39065,7 +40557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39248,7 +40744,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39309,7 +40809,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39370,7 +40874,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39431,7 +40939,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39492,7 +41004,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39614,7 +41130,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39675,7 +41195,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39736,7 +41260,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39797,7 +41325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39980,7 +41512,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40041,7 +41577,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40102,7 +41642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40163,7 +41707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40224,7 +41772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40285,7 +41837,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40346,7 +41902,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40407,7 +41967,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40468,7 +42032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40529,7 +42097,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40590,7 +42162,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40651,7 +42227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40712,7 +42292,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40773,7 +42357,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40834,7 +42422,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40895,7 +42487,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40956,7 +42552,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41017,7 +42617,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41139,7 +42743,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41322,7 +42930,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41444,7 +43056,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41505,7 +43121,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41688,7 +43308,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41749,7 +43373,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41810,7 +43438,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41871,7 +43503,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41993,7 +43629,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42054,7 +43694,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42115,7 +43759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42298,7 +43946,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42420,7 +44072,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42603,7 +44259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42664,7 +44324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42786,7 +44450,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42847,7 +44515,11 @@
           <t>77.045.877-3</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42969,7 +44641,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43030,7 +44706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/oct-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/oct-2025.xlsx
@@ -1196,7 +1196,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1513,7 +1517,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1891,7 +1899,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3663,7 +3675,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4813,7 +4829,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7987,7 +8007,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8174,7 +8198,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8556,7 +8584,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8869,7 +8901,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9828,7 +9864,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9889,7 +9929,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10137,7 +10181,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10385,7 +10433,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10767,7 +10819,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10893,7 +10949,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11653,7 +11713,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13234,7 +13298,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14054,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14184,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14234,7 +14310,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14360,7 +14440,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15563,7 +15647,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15880,7 +15968,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17140,7 +17232,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17652,7 +17748,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19408,7 +19508,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20298,7 +20402,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20741,7 +20849,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21444,7 +21556,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23740,7 +23856,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24118,7 +24238,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24374,7 +24498,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24435,7 +24563,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24870,7 +25002,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25118,7 +25254,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25614,7 +25754,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26894,7 +27038,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28414,7 +28562,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28475,7 +28627,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29044,7 +29200,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29682,7 +29842,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31096,7 +31260,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31738,7 +31906,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32181,7 +32353,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32494,7 +32670,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32937,7 +33117,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +33629,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +33759,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34018,7 +34210,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34335,7 +34531,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35290,7 +35490,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37139,7 +37343,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37521,7 +37729,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38273,7 +38485,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38399,7 +38615,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +39639,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40622,7 +40846,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41069,7 +41297,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
